--- a/templates/01_队员资料收集表.xlsx
+++ b/templates/01_队员资料收集表.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -454,13 +454,14 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -491,35 +492,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>800米</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>1500米</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>3000米</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>5000米</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>10000米</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>半马</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>全马</t>
         </is>
@@ -538,6 +544,7 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -552,6 +559,7 @@
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -566,6 +574,7 @@
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -580,18 +589,19 @@
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>填写说明：没有的项填「无」；成绩写法 1:23:29（时:分:秒）或 17:02（分:秒）；一行一个人。</t>
+          <t>填写说明：身份填 正式 / 预备 / 普通（正式、预备会显示在公开名册里，普通=队里的人但不进公开名册）；没有的项填「无」；成绩写法 1:23:29（时:分:秒）或 17:02（分:秒）；一行一个人。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>示例（别照抄，换成真实数据）：张某某 | 男 | 林学院 | 林学2101 | 2023 | 2:20 | 4:55 | 10:20 | 18:35 | 39:10 | 1:23:29 | 2:58:00</t>
+          <t>示例（别照抄，换成真实数据）：张某某 | 男 | 林学院 | 林学2101 | 2023 | 正式 | 2:20 | 4:55 | 10:20 | 18:35 | 39:10 | 1:23:29 | 2:58:00</t>
         </is>
       </c>
     </row>
